--- a/rsvp_forms/009_st_patrick_s_day_event_registration--rsvp_forms.xlsx
+++ b/rsvp_forms/009_st_patrick_s_day_event_registration--rsvp_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -543,17 +543,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>attendee_count</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Number of Attendees</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Please enter your name</t>
+          <t>Please enter total number of people attending</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -575,33 +575,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Attendee Name</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please enter attendee name</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>rsvp_choice</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>RSVP Choices</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select number of attendees you're bringing</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -611,47 +619,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rsvp_choice</t>
+          <t>event_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How many are you bringing?</t>
+          <t>Event Type</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Please choose the number of people you are bringing</t>
+          <t>Please choose event type</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rsvp_choice</t>
+          <t>event_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How many are you bringing?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select event date</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -661,22 +673,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>event_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Event Time</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Select event date</t>
+          <t>Select event time</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -688,77 +700,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter your email address</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>rsvp_type</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Type of Attendee</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Enter your email address</t>
+          <t>Please choose attendee type</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rsvp_type</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Type of Attendee</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Please choose the type of attendee</t>
+          <t>Enter your contact number</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -770,139 +786,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>event_type</t>
+          <t>payment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Please choose the event type</t>
-        </is>
-      </c>
+          <t>Payment Type</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Enter your phone number</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>rsvp_type</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Type of Attendee</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>payment</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Payment Type</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -919,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -952,12 +845,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -969,12 +862,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -986,97 +879,97 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rsvp_choice_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>event_type_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Event Type 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rsvp_choice_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>event_type_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Event Type 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rsvp_choice_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>event_type_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Event Type 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rsvp_type_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>student</t>
+          <t>event_type_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Event Type 4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rsvp_type_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>event_type_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Staff</t>
+          <t>Event Type 5</t>
         </is>
       </c>
     </row>
@@ -1088,12 +981,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1105,165 +998,80 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>faculty/staff</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faculty/Staff</t>
+          <t>Staff</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>rsvp_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>event_type_1</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Event Type 1</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>rsvp_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_type_2</t>
+          <t>faculty/staff</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Event Type 2</t>
+          <t>Faculty/Staff</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>payment_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>event_type_3</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Event Type 3</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>payment_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>event_type_4</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Event Type 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>event_type_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>event_type_5</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Event Type 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>rsvp_type_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>rsvp_type_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>payment_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>payment_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
